--- a/outputs/dados/dados_api_ibge.xlsx
+++ b/outputs/dados/dados_api_ibge.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P290"/>
+  <dimension ref="A1:P291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3446,7 +3446,7 @@
         <v>3</v>
       </c>
       <c r="C124" t="n">
-        <v>3072</v>
+        <v>3086</v>
       </c>
       <c r="D124" t="n">
         <v>1427</v>
@@ -3496,7 +3496,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="n">
-        <v>3083</v>
+        <v>3097</v>
       </c>
       <c r="D125" t="n">
         <v>1438</v>
@@ -3546,7 +3546,7 @@
         <v>5</v>
       </c>
       <c r="C126" t="n">
-        <v>3075</v>
+        <v>3089</v>
       </c>
       <c r="D126" t="n">
         <v>1440</v>
@@ -3596,7 +3596,7 @@
         <v>6</v>
       </c>
       <c r="C127" t="n">
-        <v>3082</v>
+        <v>3095</v>
       </c>
       <c r="D127" t="n">
         <v>1449</v>
@@ -3646,7 +3646,7 @@
         <v>7</v>
       </c>
       <c r="C128" t="n">
-        <v>3097</v>
+        <v>3111</v>
       </c>
       <c r="D128" t="n">
         <v>1460</v>
@@ -3696,7 +3696,7 @@
         <v>8</v>
       </c>
       <c r="C129" t="n">
-        <v>3107</v>
+        <v>3121</v>
       </c>
       <c r="D129" t="n">
         <v>1469</v>
@@ -3746,7 +3746,7 @@
         <v>9</v>
       </c>
       <c r="C130" t="n">
-        <v>3101</v>
+        <v>3115</v>
       </c>
       <c r="D130" t="n">
         <v>1473</v>
@@ -3796,7 +3796,7 @@
         <v>10</v>
       </c>
       <c r="C131" t="n">
-        <v>3097</v>
+        <v>3111</v>
       </c>
       <c r="D131" t="n">
         <v>1479</v>
@@ -3846,7 +3846,7 @@
         <v>11</v>
       </c>
       <c r="C132" t="n">
-        <v>3095</v>
+        <v>3109</v>
       </c>
       <c r="D132" t="n">
         <v>1487</v>
@@ -3896,7 +3896,7 @@
         <v>12</v>
       </c>
       <c r="C133" t="n">
-        <v>3087</v>
+        <v>3101</v>
       </c>
       <c r="D133" t="n">
         <v>1493</v>
@@ -3946,7 +3946,7 @@
         <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>3100</v>
+        <v>3114</v>
       </c>
       <c r="D134" t="n">
         <v>1511</v>
@@ -3996,7 +3996,7 @@
         <v>2</v>
       </c>
       <c r="C135" t="n">
-        <v>3118</v>
+        <v>3132</v>
       </c>
       <c r="D135" t="n">
         <v>1531</v>
@@ -4046,7 +4046,7 @@
         <v>3</v>
       </c>
       <c r="C136" t="n">
-        <v>3136</v>
+        <v>3150</v>
       </c>
       <c r="D136" t="n">
         <v>1550</v>
@@ -4096,7 +4096,7 @@
         <v>4</v>
       </c>
       <c r="C137" t="n">
-        <v>3143</v>
+        <v>3157</v>
       </c>
       <c r="D137" t="n">
         <v>1561</v>
@@ -4146,7 +4146,7 @@
         <v>5</v>
       </c>
       <c r="C138" t="n">
-        <v>3145</v>
+        <v>3159</v>
       </c>
       <c r="D138" t="n">
         <v>1570</v>
@@ -4196,7 +4196,7 @@
         <v>6</v>
       </c>
       <c r="C139" t="n">
-        <v>3171</v>
+        <v>3185</v>
       </c>
       <c r="D139" t="n">
         <v>1588</v>
@@ -4246,7 +4246,7 @@
         <v>7</v>
       </c>
       <c r="C140" t="n">
-        <v>3192</v>
+        <v>3206</v>
       </c>
       <c r="D140" t="n">
         <v>1602</v>
@@ -4296,7 +4296,7 @@
         <v>8</v>
       </c>
       <c r="C141" t="n">
-        <v>3213</v>
+        <v>3227</v>
       </c>
       <c r="D141" t="n">
         <v>1616</v>
@@ -4346,7 +4346,7 @@
         <v>9</v>
       </c>
       <c r="C142" t="n">
-        <v>3213</v>
+        <v>3227</v>
       </c>
       <c r="D142" t="n">
         <v>1619</v>
@@ -4396,7 +4396,7 @@
         <v>10</v>
       </c>
       <c r="C143" t="n">
-        <v>3222</v>
+        <v>3237</v>
       </c>
       <c r="D143" t="n">
         <v>1631</v>
@@ -4446,7 +4446,7 @@
         <v>11</v>
       </c>
       <c r="C144" t="n">
-        <v>3209</v>
+        <v>3223</v>
       </c>
       <c r="D144" t="n">
         <v>1632</v>
@@ -4496,7 +4496,7 @@
         <v>12</v>
       </c>
       <c r="C145" t="n">
-        <v>3184</v>
+        <v>3198</v>
       </c>
       <c r="D145" t="n">
         <v>1630</v>
@@ -4546,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>3180</v>
+        <v>3195</v>
       </c>
       <c r="D146" t="n">
         <v>1639</v>
@@ -4596,7 +4596,7 @@
         <v>2</v>
       </c>
       <c r="C147" t="n">
-        <v>3211</v>
+        <v>3226</v>
       </c>
       <c r="D147" t="n">
         <v>1667</v>
@@ -4646,7 +4646,7 @@
         <v>3</v>
       </c>
       <c r="C148" t="n">
-        <v>3248</v>
+        <v>3262</v>
       </c>
       <c r="D148" t="n">
         <v>1697</v>
@@ -4696,7 +4696,7 @@
         <v>4</v>
       </c>
       <c r="C149" t="n">
-        <v>3245</v>
+        <v>3260</v>
       </c>
       <c r="D149" t="n">
         <v>1709</v>
@@ -4746,7 +4746,7 @@
         <v>5</v>
       </c>
       <c r="C150" t="n">
-        <v>3239</v>
+        <v>3254</v>
       </c>
       <c r="D150" t="n">
         <v>1717</v>
@@ -4796,7 +4796,7 @@
         <v>6</v>
       </c>
       <c r="C151" t="n">
-        <v>3222</v>
+        <v>3236</v>
       </c>
       <c r="D151" t="n">
         <v>1717</v>
@@ -4846,7 +4846,7 @@
         <v>7</v>
       </c>
       <c r="C152" t="n">
-        <v>3216</v>
+        <v>3230</v>
       </c>
       <c r="D152" t="n">
         <v>1718</v>
@@ -4896,7 +4896,7 @@
         <v>8</v>
       </c>
       <c r="C153" t="n">
-        <v>3238</v>
+        <v>3253</v>
       </c>
       <c r="D153" t="n">
         <v>1734</v>
@@ -4946,7 +4946,7 @@
         <v>9</v>
       </c>
       <c r="C154" t="n">
-        <v>3249</v>
+        <v>3264</v>
       </c>
       <c r="D154" t="n">
         <v>1745</v>
@@ -4996,7 +4996,7 @@
         <v>10</v>
       </c>
       <c r="C155" t="n">
-        <v>3262</v>
+        <v>3277</v>
       </c>
       <c r="D155" t="n">
         <v>1759</v>
@@ -5046,7 +5046,7 @@
         <v>11</v>
       </c>
       <c r="C156" t="n">
-        <v>3240</v>
+        <v>3255</v>
       </c>
       <c r="D156" t="n">
         <v>1756</v>
@@ -5096,7 +5096,7 @@
         <v>12</v>
       </c>
       <c r="C157" t="n">
-        <v>3242</v>
+        <v>3256</v>
       </c>
       <c r="D157" t="n">
         <v>1767</v>
@@ -5146,7 +5146,7 @@
         <v>1</v>
       </c>
       <c r="C158" t="n">
-        <v>3246</v>
+        <v>3261</v>
       </c>
       <c r="D158" t="n">
         <v>1784</v>
@@ -5196,7 +5196,7 @@
         <v>2</v>
       </c>
       <c r="C159" t="n">
-        <v>3240</v>
+        <v>3255</v>
       </c>
       <c r="D159" t="n">
         <v>1800</v>
@@ -5246,7 +5246,7 @@
         <v>3</v>
       </c>
       <c r="C160" t="n">
-        <v>3241</v>
+        <v>3256</v>
       </c>
       <c r="D160" t="n">
         <v>1823</v>
@@ -5296,7 +5296,7 @@
         <v>4</v>
       </c>
       <c r="C161" t="n">
-        <v>3234</v>
+        <v>3248</v>
       </c>
       <c r="D161" t="n">
         <v>1839</v>
@@ -5346,7 +5346,7 @@
         <v>5</v>
       </c>
       <c r="C162" t="n">
-        <v>3219</v>
+        <v>3233</v>
       </c>
       <c r="D162" t="n">
         <v>1847</v>
@@ -5396,7 +5396,7 @@
         <v>6</v>
       </c>
       <c r="C163" t="n">
-        <v>3228</v>
+        <v>3242</v>
       </c>
       <c r="D163" t="n">
         <v>1866</v>
@@ -5446,7 +5446,7 @@
         <v>7</v>
       </c>
       <c r="C164" t="n">
-        <v>3206</v>
+        <v>3220</v>
       </c>
       <c r="D164" t="n">
         <v>1866</v>
@@ -5496,7 +5496,7 @@
         <v>8</v>
       </c>
       <c r="C165" t="n">
-        <v>3190</v>
+        <v>3204</v>
       </c>
       <c r="D165" t="n">
         <v>1868</v>
@@ -5546,7 +5546,7 @@
         <v>9</v>
       </c>
       <c r="C166" t="n">
-        <v>3188</v>
+        <v>3203</v>
       </c>
       <c r="D166" t="n">
         <v>1875</v>
@@ -5596,7 +5596,7 @@
         <v>10</v>
       </c>
       <c r="C167" t="n">
-        <v>3176</v>
+        <v>3190</v>
       </c>
       <c r="D167" t="n">
         <v>1878</v>
@@ -5646,7 +5646,7 @@
         <v>11</v>
       </c>
       <c r="C168" t="n">
-        <v>3152</v>
+        <v>3166</v>
       </c>
       <c r="D168" t="n">
         <v>1879</v>
@@ -5696,7 +5696,7 @@
         <v>12</v>
       </c>
       <c r="C169" t="n">
-        <v>3136</v>
+        <v>3150</v>
       </c>
       <c r="D169" t="n">
         <v>1887</v>
@@ -5746,7 +5746,7 @@
         <v>1</v>
       </c>
       <c r="C170" t="n">
-        <v>3146</v>
+        <v>3160</v>
       </c>
       <c r="D170" t="n">
         <v>1913</v>
@@ -5796,7 +5796,7 @@
         <v>2</v>
       </c>
       <c r="C171" t="n">
-        <v>3127</v>
+        <v>3141</v>
       </c>
       <c r="D171" t="n">
         <v>1921</v>
@@ -5846,7 +5846,7 @@
         <v>3</v>
       </c>
       <c r="C172" t="n">
-        <v>3142</v>
+        <v>3156</v>
       </c>
       <c r="D172" t="n">
         <v>1947</v>
@@ -5896,7 +5896,7 @@
         <v>4</v>
       </c>
       <c r="C173" t="n">
-        <v>3126</v>
+        <v>3140</v>
       </c>
       <c r="D173" t="n">
         <v>1950</v>
@@ -5946,7 +5946,7 @@
         <v>5</v>
       </c>
       <c r="C174" t="n">
-        <v>3137</v>
+        <v>3151</v>
       </c>
       <c r="D174" t="n">
         <v>1968</v>
@@ -5996,7 +5996,7 @@
         <v>6</v>
       </c>
       <c r="C175" t="n">
-        <v>3103</v>
+        <v>3117</v>
       </c>
       <c r="D175" t="n">
         <v>1959</v>
@@ -6046,7 +6046,7 @@
         <v>7</v>
       </c>
       <c r="C176" t="n">
-        <v>3105</v>
+        <v>3119</v>
       </c>
       <c r="D176" t="n">
         <v>1971</v>
@@ -6096,7 +6096,7 @@
         <v>8</v>
       </c>
       <c r="C177" t="n">
-        <v>3132</v>
+        <v>3146</v>
       </c>
       <c r="D177" t="n">
         <v>1996</v>
@@ -6146,7 +6146,7 @@
         <v>9</v>
       </c>
       <c r="C178" t="n">
-        <v>3129</v>
+        <v>3143</v>
       </c>
       <c r="D178" t="n">
         <v>2001</v>
@@ -6196,7 +6196,7 @@
         <v>10</v>
       </c>
       <c r="C179" t="n">
-        <v>3134</v>
+        <v>3148</v>
       </c>
       <c r="D179" t="n">
         <v>2010</v>
@@ -6246,7 +6246,7 @@
         <v>11</v>
       </c>
       <c r="C180" t="n">
-        <v>3140</v>
+        <v>3154</v>
       </c>
       <c r="D180" t="n">
         <v>2017</v>
@@ -6296,7 +6296,7 @@
         <v>12</v>
       </c>
       <c r="C181" t="n">
-        <v>3156</v>
+        <v>3170</v>
       </c>
       <c r="D181" t="n">
         <v>2032</v>
@@ -6346,7 +6346,7 @@
         <v>1</v>
       </c>
       <c r="C182" t="n">
-        <v>3167</v>
+        <v>3181</v>
       </c>
       <c r="D182" t="n">
         <v>2045</v>
@@ -6396,7 +6396,7 @@
         <v>2</v>
       </c>
       <c r="C183" t="n">
-        <v>3177</v>
+        <v>3192</v>
       </c>
       <c r="D183" t="n">
         <v>2059</v>
@@ -6446,7 +6446,7 @@
         <v>3</v>
       </c>
       <c r="C184" t="n">
-        <v>3195</v>
+        <v>3209</v>
       </c>
       <c r="D184" t="n">
         <v>2077</v>
@@ -6496,7 +6496,7 @@
         <v>4</v>
       </c>
       <c r="C185" t="n">
-        <v>3181</v>
+        <v>3195</v>
       </c>
       <c r="D185" t="n">
         <v>2072</v>
@@ -6546,7 +6546,7 @@
         <v>5</v>
       </c>
       <c r="C186" t="n">
-        <v>3176</v>
+        <v>3190</v>
       </c>
       <c r="D186" t="n">
         <v>2074</v>
@@ -6596,7 +6596,7 @@
         <v>6</v>
       </c>
       <c r="C187" t="n">
-        <v>3163</v>
+        <v>3177</v>
       </c>
       <c r="D187" t="n">
         <v>2067</v>
@@ -6646,7 +6646,7 @@
         <v>7</v>
       </c>
       <c r="C188" t="n">
-        <v>3165</v>
+        <v>3179</v>
       </c>
       <c r="D188" t="n">
         <v>2070</v>
@@ -6696,7 +6696,7 @@
         <v>8</v>
       </c>
       <c r="C189" t="n">
-        <v>3160</v>
+        <v>3174</v>
       </c>
       <c r="D189" t="n">
         <v>2068</v>
@@ -6746,7 +6746,7 @@
         <v>9</v>
       </c>
       <c r="C190" t="n">
-        <v>3176</v>
+        <v>3190</v>
       </c>
       <c r="D190" t="n">
         <v>2083</v>
@@ -6796,7 +6796,7 @@
         <v>10</v>
       </c>
       <c r="C191" t="n">
-        <v>3186</v>
+        <v>3200</v>
       </c>
       <c r="D191" t="n">
         <v>2095</v>
@@ -6846,7 +6846,7 @@
         <v>11</v>
       </c>
       <c r="C192" t="n">
-        <v>3200</v>
+        <v>3214</v>
       </c>
       <c r="D192" t="n">
         <v>2111</v>
@@ -6896,7 +6896,7 @@
         <v>12</v>
       </c>
       <c r="C193" t="n">
-        <v>3201</v>
+        <v>3215</v>
       </c>
       <c r="D193" t="n">
         <v>2120</v>
@@ -6946,7 +6946,7 @@
         <v>1</v>
       </c>
       <c r="C194" t="n">
-        <v>3212</v>
+        <v>3227</v>
       </c>
       <c r="D194" t="n">
         <v>2134</v>
@@ -6996,7 +6996,7 @@
         <v>2</v>
       </c>
       <c r="C195" t="n">
-        <v>3225</v>
+        <v>3239</v>
       </c>
       <c r="D195" t="n">
         <v>2150</v>
@@ -7046,7 +7046,7 @@
         <v>3</v>
       </c>
       <c r="C196" t="n">
-        <v>3224</v>
+        <v>3239</v>
       </c>
       <c r="D196" t="n">
         <v>2154</v>
@@ -7096,7 +7096,7 @@
         <v>4</v>
       </c>
       <c r="C197" t="n">
-        <v>3234</v>
+        <v>3249</v>
       </c>
       <c r="D197" t="n">
         <v>2165</v>
@@ -7146,7 +7146,7 @@
         <v>5</v>
       </c>
       <c r="C198" t="n">
-        <v>3236</v>
+        <v>3250</v>
       </c>
       <c r="D198" t="n">
         <v>2171</v>
@@ -7196,7 +7196,7 @@
         <v>6</v>
       </c>
       <c r="C199" t="n">
-        <v>3231</v>
+        <v>3245</v>
       </c>
       <c r="D199" t="n">
         <v>2182</v>
@@ -7246,7 +7246,7 @@
         <v>7</v>
       </c>
       <c r="C200" t="n">
-        <v>3220</v>
+        <v>3234</v>
       </c>
       <c r="D200" t="n">
         <v>2188</v>
@@ -7296,7 +7296,7 @@
         <v>8</v>
       </c>
       <c r="C201" t="n">
-        <v>3233</v>
+        <v>3248</v>
       </c>
       <c r="D201" t="n">
         <v>2208</v>
@@ -7346,7 +7346,7 @@
         <v>9</v>
       </c>
       <c r="C202" t="n">
-        <v>3220</v>
+        <v>3234</v>
       </c>
       <c r="D202" t="n">
         <v>2204</v>
@@ -7396,7 +7396,7 @@
         <v>10</v>
       </c>
       <c r="C203" t="n">
-        <v>3223</v>
+        <v>3237</v>
       </c>
       <c r="D203" t="n">
         <v>2213</v>
@@ -7446,7 +7446,7 @@
         <v>11</v>
       </c>
       <c r="C204" t="n">
-        <v>3225</v>
+        <v>3240</v>
       </c>
       <c r="D204" t="n">
         <v>2220</v>
@@ -7496,7 +7496,7 @@
         <v>12</v>
       </c>
       <c r="C205" t="n">
-        <v>3244</v>
+        <v>3258</v>
       </c>
       <c r="D205" t="n">
         <v>2236</v>
@@ -7546,7 +7546,7 @@
         <v>1</v>
       </c>
       <c r="C206" t="n">
-        <v>3264</v>
+        <v>3278</v>
       </c>
       <c r="D206" t="n">
         <v>2251</v>
@@ -7596,7 +7596,7 @@
         <v>2</v>
       </c>
       <c r="C207" t="n">
-        <v>3275</v>
+        <v>3290</v>
       </c>
       <c r="D207" t="n">
         <v>2266</v>
@@ -7646,7 +7646,7 @@
         <v>3</v>
       </c>
       <c r="C208" t="n">
-        <v>3262</v>
+        <v>3276</v>
       </c>
       <c r="D208" t="n">
         <v>2268</v>
@@ -7696,7 +7696,7 @@
         <v>4</v>
       </c>
       <c r="C209" t="n">
-        <v>3245</v>
+        <v>3259</v>
       </c>
       <c r="D209" t="n">
         <v>2269</v>
@@ -7746,7 +7746,7 @@
         <v>5</v>
       </c>
       <c r="C210" t="n">
-        <v>3222</v>
+        <v>3236</v>
       </c>
       <c r="D210" t="n">
         <v>2264</v>
@@ -7796,7 +7796,7 @@
         <v>6</v>
       </c>
       <c r="C211" t="n">
-        <v>3222</v>
+        <v>3236</v>
       </c>
       <c r="D211" t="n">
         <v>2270</v>
@@ -7846,7 +7846,7 @@
         <v>7</v>
       </c>
       <c r="C212" t="n">
-        <v>3214</v>
+        <v>3229</v>
       </c>
       <c r="D212" t="n">
         <v>2267</v>
@@ -7896,7 +7896,7 @@
         <v>8</v>
       </c>
       <c r="C213" t="n">
-        <v>3227</v>
+        <v>3242</v>
       </c>
       <c r="D213" t="n">
         <v>2278</v>
@@ -7946,7 +7946,7 @@
         <v>9</v>
       </c>
       <c r="C214" t="n">
-        <v>3226</v>
+        <v>3241</v>
       </c>
       <c r="D214" t="n">
         <v>2279</v>
@@ -7996,7 +7996,7 @@
         <v>10</v>
       </c>
       <c r="C215" t="n">
-        <v>3250</v>
+        <v>3265</v>
       </c>
       <c r="D215" t="n">
         <v>2297</v>
@@ -8046,7 +8046,7 @@
         <v>11</v>
       </c>
       <c r="C216" t="n">
-        <v>3264</v>
+        <v>3279</v>
       </c>
       <c r="D216" t="n">
         <v>2312</v>
@@ -8096,7 +8096,7 @@
         <v>12</v>
       </c>
       <c r="C217" t="n">
-        <v>3254</v>
+        <v>3268</v>
       </c>
       <c r="D217" t="n">
         <v>2319</v>
@@ -8146,7 +8146,7 @@
         <v>1</v>
       </c>
       <c r="C218" t="n">
-        <v>3261</v>
+        <v>3276</v>
       </c>
       <c r="D218" t="n">
         <v>2338</v>
@@ -8196,7 +8196,7 @@
         <v>2</v>
       </c>
       <c r="C219" t="n">
-        <v>3264</v>
+        <v>3279</v>
       </c>
       <c r="D219" t="n">
         <v>2353</v>
@@ -8246,7 +8246,7 @@
         <v>3</v>
       </c>
       <c r="C220" t="n">
-        <v>3291</v>
+        <v>3306</v>
       </c>
       <c r="D220" t="n">
         <v>2376</v>
@@ -8296,7 +8296,7 @@
         <v>4</v>
       </c>
       <c r="C221" t="n">
-        <v>3327</v>
+        <v>3342</v>
       </c>
       <c r="D221" t="n">
         <v>2402</v>
@@ -8346,7 +8346,7 @@
         <v>5</v>
       </c>
       <c r="C222" t="n">
-        <v>3381</v>
+        <v>3396</v>
       </c>
       <c r="D222" t="n">
         <v>2437</v>
@@ -8396,7 +8396,7 @@
         <v>6</v>
       </c>
       <c r="C223" t="n">
-        <v>3434</v>
+        <v>3449</v>
       </c>
       <c r="D223" t="n">
         <v>2471</v>
@@ -8446,7 +8446,7 @@
         <v>7</v>
       </c>
       <c r="C224" t="n">
-        <v>3474</v>
+        <v>3490</v>
       </c>
       <c r="D224" t="n">
         <v>2502</v>
@@ -8496,7 +8496,7 @@
         <v>8</v>
       </c>
       <c r="C225" t="n">
-        <v>3469</v>
+        <v>3485</v>
       </c>
       <c r="D225" t="n">
         <v>2506</v>
@@ -8546,7 +8546,7 @@
         <v>9</v>
       </c>
       <c r="C226" t="n">
-        <v>3472</v>
+        <v>3487</v>
       </c>
       <c r="D226" t="n">
         <v>2517</v>
@@ -8596,7 +8596,7 @@
         <v>10</v>
       </c>
       <c r="C227" t="n">
-        <v>3420</v>
+        <v>3436</v>
       </c>
       <c r="D227" t="n">
         <v>2495</v>
@@ -8646,7 +8646,7 @@
         <v>11</v>
       </c>
       <c r="C228" t="n">
-        <v>3384</v>
+        <v>3399</v>
       </c>
       <c r="D228" t="n">
         <v>2488</v>
@@ -8696,7 +8696,7 @@
         <v>12</v>
       </c>
       <c r="C229" t="n">
-        <v>3332</v>
+        <v>3347</v>
       </c>
       <c r="D229" t="n">
         <v>2476</v>
@@ -8746,7 +8746,7 @@
         <v>1</v>
       </c>
       <c r="C230" t="n">
-        <v>3325</v>
+        <v>3339</v>
       </c>
       <c r="D230" t="n">
         <v>2491</v>
@@ -8796,7 +8796,7 @@
         <v>2</v>
       </c>
       <c r="C231" t="n">
-        <v>3294</v>
+        <v>3309</v>
       </c>
       <c r="D231" t="n">
         <v>2488</v>
@@ -8846,7 +8846,7 @@
         <v>3</v>
       </c>
       <c r="C232" t="n">
-        <v>3304</v>
+        <v>3318</v>
       </c>
       <c r="D232" t="n">
         <v>2512</v>
@@ -8896,7 +8896,7 @@
         <v>4</v>
       </c>
       <c r="C233" t="n">
-        <v>3264</v>
+        <v>3279</v>
       </c>
       <c r="D233" t="n">
         <v>2500</v>
@@ -8946,7 +8946,7 @@
         <v>5</v>
       </c>
       <c r="C234" t="n">
-        <v>3261</v>
+        <v>3276</v>
       </c>
       <c r="D234" t="n">
         <v>2515</v>
@@ -8996,7 +8996,7 @@
         <v>6</v>
       </c>
       <c r="C235" t="n">
-        <v>3210</v>
+        <v>3224</v>
       </c>
       <c r="D235" t="n">
         <v>2490</v>
@@ -9046,7 +9046,7 @@
         <v>7</v>
       </c>
       <c r="C236" t="n">
-        <v>3180</v>
+        <v>3194</v>
       </c>
       <c r="D236" t="n">
         <v>2485</v>
@@ -9096,7 +9096,7 @@
         <v>8</v>
       </c>
       <c r="C237" t="n">
-        <v>3135</v>
+        <v>3149</v>
       </c>
       <c r="D237" t="n">
         <v>2469</v>
@@ -9146,7 +9146,7 @@
         <v>9</v>
       </c>
       <c r="C238" t="n">
-        <v>3080</v>
+        <v>3093</v>
       </c>
       <c r="D238" t="n">
         <v>2450</v>
@@ -9196,7 +9196,7 @@
         <v>10</v>
       </c>
       <c r="C239" t="n">
-        <v>3035</v>
+        <v>3048</v>
       </c>
       <c r="D239" t="n">
         <v>2440</v>
@@ -9246,7 +9246,7 @@
         <v>11</v>
       </c>
       <c r="C240" t="n">
-        <v>2994</v>
+        <v>3008</v>
       </c>
       <c r="D240" t="n">
         <v>2435</v>
@@ -9296,7 +9296,7 @@
         <v>12</v>
       </c>
       <c r="C241" t="n">
-        <v>2970</v>
+        <v>2984</v>
       </c>
       <c r="D241" t="n">
         <v>2439</v>
@@ -9346,7 +9346,7 @@
         <v>1</v>
       </c>
       <c r="C242" t="n">
-        <v>2998</v>
+        <v>3011</v>
       </c>
       <c r="D242" t="n">
         <v>2480</v>
@@ -9396,7 +9396,7 @@
         <v>2</v>
       </c>
       <c r="C243" t="n">
-        <v>3002</v>
+        <v>3015</v>
       </c>
       <c r="D243" t="n">
         <v>2501</v>
@@ -9446,7 +9446,7 @@
         <v>3</v>
       </c>
       <c r="C244" t="n">
-        <v>3014</v>
+        <v>3027</v>
       </c>
       <c r="D244" t="n">
         <v>2538</v>
@@ -9496,7 +9496,7 @@
         <v>4</v>
       </c>
       <c r="C245" t="n">
-        <v>3002</v>
+        <v>3016</v>
       </c>
       <c r="D245" t="n">
         <v>2559</v>
@@ -9546,7 +9546,7 @@
         <v>5</v>
       </c>
       <c r="C246" t="n">
-        <v>3021</v>
+        <v>3035</v>
       </c>
       <c r="D246" t="n">
         <v>2602</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C247" t="n">
-        <v>3043</v>
+        <v>3057</v>
       </c>
       <c r="D247" t="n">
         <v>2641</v>
@@ -9646,7 +9646,7 @@
         <v>7</v>
       </c>
       <c r="C248" t="n">
-        <v>3086</v>
+        <v>3100</v>
       </c>
       <c r="D248" t="n">
         <v>2681</v>
@@ -9696,7 +9696,7 @@
         <v>8</v>
       </c>
       <c r="C249" t="n">
-        <v>3113</v>
+        <v>3127</v>
       </c>
       <c r="D249" t="n">
         <v>2701</v>
@@ -9746,7 +9746,7 @@
         <v>9</v>
       </c>
       <c r="C250" t="n">
-        <v>3156</v>
+        <v>3169</v>
       </c>
       <c r="D250" t="n">
         <v>2725</v>
@@ -9796,7 +9796,7 @@
         <v>10</v>
       </c>
       <c r="C251" t="n">
-        <v>3174</v>
+        <v>3188</v>
       </c>
       <c r="D251" t="n">
         <v>2741</v>
@@ -9846,7 +9846,7 @@
         <v>11</v>
       </c>
       <c r="C252" t="n">
-        <v>3205</v>
+        <v>3219</v>
       </c>
       <c r="D252" t="n">
         <v>2774</v>
@@ -9896,7 +9896,7 @@
         <v>12</v>
       </c>
       <c r="C253" t="n">
-        <v>3212</v>
+        <v>3226</v>
       </c>
       <c r="D253" t="n">
         <v>2795</v>
@@ -9946,7 +9946,7 @@
         <v>1</v>
       </c>
       <c r="C254" t="n">
-        <v>3226</v>
+        <v>3240</v>
       </c>
       <c r="D254" t="n">
         <v>2821</v>
@@ -9996,7 +9996,7 @@
         <v>2</v>
       </c>
       <c r="C255" t="n">
-        <v>3224</v>
+        <v>3238</v>
       </c>
       <c r="D255" t="n">
         <v>2839</v>
@@ -10046,7 +10046,7 @@
         <v>3</v>
       </c>
       <c r="C256" t="n">
-        <v>3232</v>
+        <v>3246</v>
       </c>
       <c r="D256" t="n">
         <v>2865</v>
@@ -10096,7 +10096,7 @@
         <v>4</v>
       </c>
       <c r="C257" t="n">
-        <v>3222</v>
+        <v>3236</v>
       </c>
       <c r="D257" t="n">
         <v>2876</v>
@@ -10146,7 +10146,7 @@
         <v>5</v>
       </c>
       <c r="C258" t="n">
-        <v>3216</v>
+        <v>3230</v>
       </c>
       <c r="D258" t="n">
         <v>2886</v>
@@ -10196,7 +10196,7 @@
         <v>6</v>
       </c>
       <c r="C259" t="n">
-        <v>3231</v>
+        <v>3245</v>
       </c>
       <c r="D259" t="n">
         <v>2906</v>
@@ -10246,7 +10246,7 @@
         <v>7</v>
       </c>
       <c r="C260" t="n">
-        <v>3242</v>
+        <v>3256</v>
       </c>
       <c r="D260" t="n">
         <v>2919</v>
@@ -10296,7 +10296,7 @@
         <v>8</v>
       </c>
       <c r="C261" t="n">
-        <v>3252</v>
+        <v>3266</v>
       </c>
       <c r="D261" t="n">
         <v>2931</v>
@@ -10346,7 +10346,7 @@
         <v>9</v>
       </c>
       <c r="C262" t="n">
-        <v>3283</v>
+        <v>3298</v>
       </c>
       <c r="D262" t="n">
         <v>2965</v>
@@ -10396,7 +10396,7 @@
         <v>10</v>
       </c>
       <c r="C263" t="n">
-        <v>3295</v>
+        <v>3309</v>
       </c>
       <c r="D263" t="n">
         <v>2983</v>
@@ -10446,7 +10446,7 @@
         <v>11</v>
       </c>
       <c r="C264" t="n">
-        <v>3323</v>
+        <v>3338</v>
       </c>
       <c r="D264" t="n">
         <v>3016</v>
@@ -10496,7 +10496,7 @@
         <v>12</v>
       </c>
       <c r="C265" t="n">
-        <v>3309</v>
+        <v>3324</v>
       </c>
       <c r="D265" t="n">
         <v>3014</v>
@@ -10546,7 +10546,7 @@
         <v>1</v>
       </c>
       <c r="C266" t="n">
-        <v>3346</v>
+        <v>3361</v>
       </c>
       <c r="D266" t="n">
         <v>3061</v>
@@ -10596,7 +10596,7 @@
         <v>2</v>
       </c>
       <c r="C267" t="n">
-        <v>3361</v>
+        <v>3376</v>
       </c>
       <c r="D267" t="n">
         <v>3093</v>
@@ -10646,7 +10646,7 @@
         <v>3</v>
       </c>
       <c r="C268" t="n">
-        <v>3358</v>
+        <v>3373</v>
       </c>
       <c r="D268" t="n">
         <v>3105</v>
@@ -10696,7 +10696,7 @@
         <v>4</v>
       </c>
       <c r="C269" t="n">
-        <v>3373</v>
+        <v>3388</v>
       </c>
       <c r="D269" t="n">
         <v>3133</v>
@@ -10746,7 +10746,7 @@
         <v>5</v>
       </c>
       <c r="C270" t="n">
-        <v>3394</v>
+        <v>3409</v>
       </c>
       <c r="D270" t="n">
         <v>3163</v>
@@ -10796,7 +10796,7 @@
         <v>6</v>
       </c>
       <c r="C271" t="n">
-        <v>3415</v>
+        <v>3431</v>
       </c>
       <c r="D271" t="n">
         <v>3194</v>
@@ -10846,7 +10846,7 @@
         <v>7</v>
       </c>
       <c r="C272" t="n">
-        <v>3396</v>
+        <v>3411</v>
       </c>
       <c r="D272" t="n">
         <v>3187</v>
@@ -10896,7 +10896,7 @@
         <v>8</v>
       </c>
       <c r="C273" t="n">
-        <v>3413</v>
+        <v>3429</v>
       </c>
       <c r="D273" t="n">
         <v>3209</v>
@@ -10946,7 +10946,7 @@
         <v>9</v>
       </c>
       <c r="C274" t="n">
-        <v>3402</v>
+        <v>3417</v>
       </c>
       <c r="D274" t="n">
         <v>3207</v>
@@ -10996,7 +10996,7 @@
         <v>10</v>
       </c>
       <c r="C275" t="n">
-        <v>3421</v>
+        <v>3436</v>
       </c>
       <c r="D275" t="n">
         <v>3235</v>
@@ -11046,7 +11046,7 @@
         <v>11</v>
       </c>
       <c r="C276" t="n">
-        <v>3436</v>
+        <v>3451</v>
       </c>
       <c r="D276" t="n">
         <v>3264</v>
@@ -11096,7 +11096,7 @@
         <v>12</v>
       </c>
       <c r="C277" t="n">
-        <v>3450</v>
+        <v>3465</v>
       </c>
       <c r="D277" t="n">
         <v>3293</v>
@@ -11146,7 +11146,7 @@
         <v>1</v>
       </c>
       <c r="C278" t="n">
-        <v>3466</v>
+        <v>3482</v>
       </c>
       <c r="D278" t="n">
         <v>3321</v>
@@ -11196,7 +11196,7 @@
         <v>2</v>
       </c>
       <c r="C279" t="n">
-        <v>3480</v>
+        <v>3495</v>
       </c>
       <c r="D279" t="n">
         <v>3356</v>
@@ -11246,7 +11246,7 @@
         <v>3</v>
       </c>
       <c r="C280" t="n">
-        <v>3490</v>
+        <v>3505</v>
       </c>
       <c r="D280" t="n">
         <v>3389</v>
@@ -11296,7 +11296,7 @@
         <v>4</v>
       </c>
       <c r="C281" t="n">
-        <v>3479</v>
+        <v>3494</v>
       </c>
       <c r="D281" t="n">
         <v>3404</v>
@@ -11346,7 +11346,7 @@
         <v>5</v>
       </c>
       <c r="C282" t="n">
-        <v>3494</v>
+        <v>3509</v>
       </c>
       <c r="D282" t="n">
         <v>3433</v>
@@ -11396,7 +11396,7 @@
         <v>6</v>
       </c>
       <c r="C283" t="n">
-        <v>3527</v>
+        <v>3543</v>
       </c>
       <c r="D283" t="n">
         <v>3477</v>
@@ -11446,7 +11446,7 @@
         <v>7</v>
       </c>
       <c r="C284" t="n">
-        <v>3525</v>
+        <v>3541</v>
       </c>
       <c r="D284" t="n">
         <v>3484</v>
@@ -11496,7 +11496,7 @@
         <v>8</v>
       </c>
       <c r="C285" t="n">
-        <v>3525</v>
+        <v>3541</v>
       </c>
       <c r="D285" t="n">
         <v>3488</v>
@@ -11546,7 +11546,7 @@
         <v>9</v>
       </c>
       <c r="C286" t="n">
-        <v>3537</v>
+        <v>3552</v>
       </c>
       <c r="D286" t="n">
         <v>3507</v>
@@ -11596,7 +11596,7 @@
         <v>10</v>
       </c>
       <c r="C287" t="n">
-        <v>3553</v>
+        <v>3568</v>
       </c>
       <c r="D287" t="n">
         <v>3528</v>
@@ -11646,7 +11646,7 @@
         <v>11</v>
       </c>
       <c r="C288" t="n">
-        <v>3591</v>
+        <v>3606</v>
       </c>
       <c r="D288" t="n">
         <v>3574</v>
@@ -11696,7 +11696,7 @@
         <v>12</v>
       </c>
       <c r="C289" t="n">
-        <v>3623</v>
+        <v>3639</v>
       </c>
       <c r="D289" t="n">
         <v>3613</v>
@@ -11746,7 +11746,7 @@
         <v>1</v>
       </c>
       <c r="C290" t="n">
-        <v>3652</v>
+        <v>3668</v>
       </c>
       <c r="D290" t="n">
         <v>3652</v>
@@ -11786,6 +11786,54 @@
       </c>
       <c r="P290" t="n">
         <v>60990</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B291" t="n">
+        <v>2</v>
+      </c>
+      <c r="C291" t="n">
+        <v>3679</v>
+      </c>
+      <c r="D291" t="n">
+        <v>3679</v>
+      </c>
+      <c r="E291" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F291" t="n">
+        <v>102145</v>
+      </c>
+      <c r="G291" t="n">
+        <v>39220</v>
+      </c>
+      <c r="H291" t="n">
+        <v>13290</v>
+      </c>
+      <c r="I291" t="n">
+        <v>5490</v>
+      </c>
+      <c r="J291" t="n">
+        <v>12620</v>
+      </c>
+      <c r="K291" t="n">
+        <v>4209</v>
+      </c>
+      <c r="L291" t="n">
+        <v>26108</v>
+      </c>
+      <c r="M291" t="n">
+        <v>1207</v>
+      </c>
+      <c r="N291" t="inlineStr"/>
+      <c r="O291" t="n">
+        <v>41317</v>
+      </c>
+      <c r="P291" t="n">
+        <v>60828</v>
       </c>
     </row>
   </sheetData>
